--- a/output/P1.xlsx
+++ b/output/P1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="task-1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="task-2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="task-3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="task-4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="task-1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="task-2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="task-3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="task-4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1582,24 +1582,24 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33">
-        <f>== Cell 1 outputs ===
-Games selected: 3,843
-Selected games by genre:
-Selected records with missing or invalid prices: 0
-Mean price comparison by genre:
-           genre  game_count  valid_price_count mean_price median_price
-rank                                                                   
-1         Sports          63                 63     $13.80        $8.99
-2            RPG         270                270     $11.97        $8.15
-3     Simulation         328                328     $10.87        $6.99
-4       Strategy         485                485     $10.41        $6.99
-5         Action         843                843      $9.98        $6.99
-6      Adventure         535                535      $8.73        $6.99
-7         Casual         560                560      $4.68        $3.99
-8          Indie         759                759      $3.97        $2.89
-Final result:
-Genre with the highest average price: Sports
-Highest average price: $13.80
+        <f>== Cell 1 outputs ===
+Games selected: 3,843
+Selected games by genre:
+Selected records with missing or invalid prices: 0
+Mean price comparison by genre:
+           genre  game_count  valid_price_count mean_price median_price
+rank                                                                   
+1         Sports          63                 63     $13.80        $8.99
+2            RPG         270                270     $11.97        $8.15
+3     Simulation         328                328     $10.87        $6.99
+4       Strategy         485                485     $10.41        $6.99
+5         Action         843                843      $9.98        $6.99
+6      Adventure         535                535      $8.73        $6.99
+7         Casual         560                560      $4.68        $3.99
+8          Indie         759                759      $3.97        $2.89
+Final result:
+Genre with the highest average price: Sports
+Highest average price: $13.80
 &lt;Figure size 800x500 with 1 Axes&gt;</f>
         <v/>
       </c>
@@ -1629,24 +1629,24 @@
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34">
-        <f>== Cell 1 outputs ===
-Games selected: 3,843
-Selected games by genre:
-Selected records with missing or invalid prices: 0
-Mean price comparison by genre:
-           genre  game_count  valid_price_count mean_price median_price
-rank                                                                   
-1         Sports          63                 63     $13.80        $8.99
-2            RPG         270                270     $11.97        $8.15
-3     Simulation         328                328     $10.87        $6.99
-4       Strategy         485                485     $10.41        $6.99
-5         Action         843                843      $9.98        $6.99
-6      Adventure         535                535      $8.73        $6.99
-7         Casual         560                560      $4.68        $3.99
-8          Indie         759                759      $3.97        $2.89
-Final result:
-Genre with the highest average price: Sports
-Highest average price: $13.80
+        <f>== Cell 1 outputs ===
+Games selected: 3,843
+Selected games by genre:
+Selected records with missing or invalid prices: 0
+Mean price comparison by genre:
+           genre  game_count  valid_price_count mean_price median_price
+rank                                                                   
+1         Sports          63                 63     $13.80        $8.99
+2            RPG         270                270     $11.97        $8.15
+3     Simulation         328                328     $10.87        $6.99
+4       Strategy         485                485     $10.41        $6.99
+5         Action         843                843      $9.98        $6.99
+6      Adventure         535                535      $8.73        $6.99
+7         Casual         560                560      $4.68        $3.99
+8          Indie         759                759      $3.97        $2.89
+Final result:
+Genre with the highest average price: Sports
+Highest average price: $13.80
 &lt;Figure size 800x500 with 1 Axes&gt;</f>
         <v/>
       </c>
@@ -2426,13 +2426,13 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Loading...
-Loaded: (27075, 18)
-Filtering...
-Filtered: (27075, 18)
-Computing ratio...
-Running Pearson...
-Correlation: 0.07645489290365289
+          <t>Loading...
+Loaded: (27075, 18)
+Filtering...
+Filtered: (27075, 18)
+Computing ratio...
+Running Pearson...
+Correlation: 0.07645489290365289
 P-value: 2.1624296513817798e-36</t>
         </is>
       </c>
@@ -2463,13 +2463,13 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Loading...
-Loaded: (27075, 18)
-Filtering...
-Filtered: (27075, 18)
-Computing ratio...
-Running Pearson...
-Correlation: 0.07645489290365289
+          <t>Loading...
+Loaded: (27075, 18)
+Filtering...
+Filtered: (27075, 18)
+Computing ratio...
+Running Pearson...
+Correlation: 0.07645489290365289
 P-value: 2.1624296513817798e-36</t>
         </is>
       </c>
@@ -2864,7 +2864,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0 markdown 'The publisher pricing strategy team wants to understand whet'
+          <t>0 markdown 'The publisher pricing strategy team wants to understand whet'
 1 code 'from pathlib import Path\n\nimport matplotlib.pyplot as plt\nim'</t>
         </is>
       </c>
@@ -2895,7 +2895,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0 markdown 'The publisher pricing strategy team wants to understand whet'
+          <t>0 markdown 'The publisher pricing strategy team wants to understand whet'
 1 code 'from pathlib import Path\n\nimport matplotlib.pyplot as plt\nim'</t>
         </is>
       </c>
@@ -2986,100 +2986,100 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>Base directory for this skill: C:\Users\sani2\AppData\Local\Temp\claude\bundled-skills\2.1.218\2adb0078869583fb87c275b8fa18eb58\dataviz
-# Data Visualization
-A chart is **read by people and executed by you**. This skill turns "make it look
-good" into a procedure with checks, so the result is right by construction rather
-than by taste.
-**The method here is design-system-agnostic.** Nothing in the procedure, the form
-heuristic, the six checks, or the mark specs is specific to one product. A design
-system supplies a small set of *parameters* (its ramps, a categorical order, a
-diverging pair, a status palette, a texture, its surfaces, its filter components);
-the method consumes them unchanged. A **validated default palette** is the
-reference instance, fully specified in `references/palette.md`. To target your
-brand, read that file's structure and substitute its values — touch nothing else.
-&gt; The single most important habit: **the color part is computable, so compute it.**
-&gt; Never eyeball whether a palette is colorblind-safe — run `scripts/validate_palette.js`.
-## The procedure — do these in order
-Color comes LAST. Most bad charts pick colors first.
-1. **Pick the form.** What is the data's job — magnitude, identity, polarity, a
-   single headline, change-over-time? The job picks the chart type, and sometimes
-   the answer is *not a chart* (a stat tile or hero number). → `references/choosing-a-form.md`
-2. **Assign color by the job it does.** Categorical (identity), sequential
-   (magnitude), diverging (polarity), or status (state) — each has one rule.
-   Assign categorical hues in fixed order, never cycled. → `references/color-formula.md`
-3. **VALIDATE the palette — run the script, don't reason about ΔE.**
-   `node scripts/validate_palette.js "&lt;hex,hex,…&gt;" --mode light` (relative to
-   this skill's base directory — or load it as `&lt;script type="module"&gt;` in the
-   chart's own page, where it reads
-   `data-palette` off `&lt;body&gt;` and logs a `console.table` report). It returns
-   pass/fail on the lightness band, chroma floor, adjacent-pair CVD separation,
-   the normal-vision floor, and contrast. Fix anything that FAILs before continuing. Re-run for
-   `--mode dark` with that mode's surface.
-4. **Apply mark specs &amp; spacers.** Thin marks, 4px rounded data-ends anchored to
-   the baseline, 2px lines, ≥8px markers, a 2px surface gap between fills (stacked
-   segments and adjacent bars alike) and a 2px surface ring on overlapping marks,
-   selective direct labels. → `references/marks-and-anatomy.md`
-5. **Add the hover layer — by default.** An HTML/SVG chart *is* interactive; ship
-   a crosshair+tooltip on line/area and a per-mark hover tooltip on bar/dot/cell.
-   The only form that skips it is a bare stat tile with no plot. Hit targets bigger
-   than the mark; filters in one row above the charts. → `references/interaction.md`
-6. **Final accessibility pass.** For ≥ 2 series a legend is always present and ≤ 4
-   are also direct-labeled (a single series needs no legend box — the title names
-   it), so identity is never color-alone; a table view exists; dark mode is **selected** — its own
-   steps from the same ramps, validated against the dark surface, not an automatic
-   flip; texture is available for the CVD/print/forced-colors case.
-7. **Render it and look at it.** The validator checks color, not layout — open or
-   screenshot the output and eyeball it for label collisions, geometry, and overflow
-   before calling it done.
-Then check the result against **`references/anti-patterns.md`** — it is the catalog
-of what goes wrong. If your chart matches an entry, it's wrong.
-## Non-negotiables (true in every design system)
-- **Assign categorical hues in fixed order, never cycled.** A 9th series is never a
-  generated hue — it folds into "Other," small multiples, or composite encoding.
-- **One axis.** Never a dual-axis chart (two y-scales). Two measures of different
-  scale → two charts, small multiples, or indexed to a common base. *(This is the
-  #1 chart mistake — see anti-patterns.)*
-- **Color follows the entity, never its rank.** A filter that changes the series
-  count must not repaint the survivors.
-- **Sequential = one hue, light→dark. Diverging = two hues + a neutral gray
-  midpoint.** Never a rainbow; never a hue at the diverging midpoint.
-- **Run the validator before shipping any categorical palette.** CVD ΔE ≥ 8 is the
-  target (OKLab ×100); 6–8 is a floor that is legal ONLY with secondary encoding. A
-  normal-vision floor below 15 is a hard FAIL — full-color readers can't tell the
-  pair apart; re-step it on the adjacent pairlist (secondary encoding does not excuse
-  this one); under `--pairs all` cut series or facet instead — see check 4. A contrast WARN
-  obligates visible labels or a table view — it is not dismissable.
-- **Thin marks; a legend always present for ≥ 2 series (none for one), with
-  selective direct labels (never a number on every point); recessive grid/axes.**
-- **Text wears text tokens, never the series color** — values, labels, and legends
-  stay in primary/secondary/muted ink; a colored mark beside them carries identity.
-- **Status colors are reserved** (good/warning/serious/critical) and never reused
-  for "series 4"; they ship with an icon + label, never color alone.
-## Plugging in a design system
-The method is invariant; only these parameters change per system. The reference
-instance — every value filled in — is `references/palette.md`.
-| Parameter | What the system provides |
-|---|---|
-| **Ramps** | the hue scales (named steps) the palette draws from |
-| **Categorical theme** | the fixed hue order (a named theme); default + alternates |
-| **Sequential hue** | the default single hue for magnitude |
-| **Diverging pair** | two warm/cool poles + a neutral midpoint |
-| **Status palette** | good / warning / serious / critical — steps distinct from categorical |
-| **Texture fill** | one directional hand-drawn fill, used at 45° / 135° |
-| **Surfaces** | light &amp; dark chart-surface colors (the validator needs these) |
-| **Filter controls** | date-range &amp; dimension controls (behavioral spec in `interaction.md`) |
-To onboard a new system: fill those rows, feed its ramps to the validator, and let
-it snap each slot to the nearest passing step. Structure and rules stay as written.
-## Reference files
-| File | What it answers |
-|------|-----------------|
-| `references/choosing-a-form.md` | Which chart type / is it even a chart? |
-| `references/color-formula.md` | The four jobs, the six checks, snap-to-passing |
-| `references/marks-and-anatomy.md` | Mark specs, spacers, labels, figures, hero number |
-| `references/interaction.md` | Tooltips &amp; hover, filters &amp; time ranges |
-| `references/components.md` | The pieces a chart is made of — build each in plain HTML |
-| `references/anti-patterns.md` | **What goes wrong — check every chart against this** |
-| `references/palette.md` | **The reference palette instance** — every parameter, filled in; swap for your brand's |
+# Data Visualization
+A chart is **read by people and executed by you**. This skill turns "make it look
+good" into a procedure with checks, so the result is right by construction rather
+than by taste.
+**The method here is design-system-agnostic.** Nothing in the procedure, the form
+heuristic, the six checks, or the mark specs is specific to one product. A design
+system supplies a small set of *parameters* (its ramps, a categorical order, a
+diverging pair, a status palette, a texture, its surfaces, its filter components);
+the method consumes them unchanged. A **validated default palette** is the
+reference instance, fully specified in `references/palette.md`. To target your
+brand, read that file's structure and substitute its values — touch nothing else.
+&gt; The single most important habit: **the color part is computable, so compute it.**
+&gt; Never eyeball whether a palette is colorblind-safe — run `scripts/validate_palette.js`.
+## The procedure — do these in order
+Color comes LAST. Most bad charts pick colors first.
+1. **Pick the form.** What is the data's job — magnitude, identity, polarity, a
+   single headline, change-over-time? The job picks the chart type, and sometimes
+   the answer is *not a chart* (a stat tile or hero number). → `references/choosing-a-form.md`
+2. **Assign color by the job it does.** Categorical (identity), sequential
+   (magnitude), diverging (polarity), or status (state) — each has one rule.
+   Assign categorical hues in fixed order, never cycled. → `references/color-formula.md`
+3. **VALIDATE the palette — run the script, don't reason about ΔE.**
+   `node scripts/validate_palette.js "&lt;hex,hex,…&gt;" --mode light` (relative to
+   this skill's base directory — or load it as `&lt;script type="module"&gt;` in the
+   chart's own page, where it reads
+   `data-palette` off `&lt;body&gt;` and logs a `console.table` report). It returns
+   pass/fail on the lightness band, chroma floor, adjacent-pair CVD separation,
+   the normal-vision floor, and contrast. Fix anything that FAILs before continuing. Re-run for
+   `--mode dark` with that mode's surface.
+4. **Apply mark specs &amp; spacers.** Thin marks, 4px rounded data-ends anchored to
+   the baseline, 2px lines, ≥8px markers, a 2px surface gap between fills (stacked
+   segments and adjacent bars alike) and a 2px surface ring on overlapping marks,
+   selective direct labels. → `references/marks-and-anatomy.md`
+5. **Add the hover layer — by default.** An HTML/SVG chart *is* interactive; ship
+   a crosshair+tooltip on line/area and a per-mark hover tooltip on bar/dot/cell.
+   The only form that skips it is a bare stat tile with no plot. Hit targets bigger
+   than the mark; filters in one row above the charts. → `references/interaction.md`
+6. **Final accessibility pass.** For ≥ 2 series a legend is always present and ≤ 4
+   are also direct-labeled (a single series needs no legend box — the title names
+   it), so identity is never color-alone; a table view exists; dark mode is **selected** — its own
+   steps from the same ramps, validated against the dark surface, not an automatic
+   flip; texture is available for the CVD/print/forced-colors case.
+7. **Render it and look at it.** The validator checks color, not layout — open or
+   screenshot the output and eyeball it for label collisions, geometry, and overflow
+   before calling it done.
+Then check the result against **`references/anti-patterns.md`** — it is the catalog
+of what goes wrong. If your chart matches an entry, it's wrong.
+## Non-negotiables (true in every design system)
+- **Assign categorical hues in fixed order, never cycled.** A 9th series is never a
+  generated hue — it folds into "Other," small multiples, or composite encoding.
+- **One axis.** Never a dual-axis chart (two y-scales). Two measures of different
+  scale → two charts, small multiples, or indexed to a common base. *(This is the
+  #1 chart mistake — see anti-patterns.)*
+- **Color follows the entity, never its rank.** A filter that changes the series
+  count must not repaint the survivors.
+- **Sequential = one hue, light→dark. Diverging = two hues + a neutral gray
+  midpoint.** Never a rainbow; never a hue at the diverging midpoint.
+- **Run the validator before shipping any categorical palette.** CVD ΔE ≥ 8 is the
+  target (OKLab ×100); 6–8 is a floor that is legal ONLY with secondary encoding. A
+  normal-vision floor below 15 is a hard FAIL — full-color readers can't tell the
+  pair apart; re-step it on the adjacent pairlist (secondary encoding does not excuse
+  this one); under `--pairs all` cut series or facet instead — see check 4. A contrast WARN
+  obligates visible labels or a table view — it is not dismissable.
+- **Thin marks; a legend always present for ≥ 2 series (none for one), with
+  selective direct labels (never a number on every point); recessive grid/axes.**
+- **Text wears text tokens, never the series color** — values, labels, and legends
+  stay in primary/secondary/muted ink; a colored mark beside them carries identity.
+- **Status colors are reserved** (good/warning/serious/critical) and never reused
+  for "series 4"; they ship with an icon + label, never color alone.
+## Plugging in a design system
+The method is invariant; only these parameters change per system. The reference
+instance — every value filled in — is `references/palette.md`.
+| Parameter | What the system provides |
+|---|---|
+| **Ramps** | the hue scales (named steps) the palette draws from |
+| **Categorical theme** | the fixed hue order (a named theme); default + alternates |
+| **Sequential hue** | the default single hue for magnitude |
+| **Diverging pair** | two warm/cool poles + a neutral midpoint |
+| **Status palette** | good / warning / serious / critical — steps distinct from categorical |
+| **Texture fill** | one directional hand-drawn fill, used at 45° / 135° |
+| **Surfaces** | light &amp; dark chart-surface colors (the validator needs these) |
+| **Filter controls** | date-range &amp; dimension controls (behavioral spec in `interaction.md`) |
+To onboard a new system: fill those rows, feed its ramps to the validator, and let
+it snap each slot to the nearest passing step. Structure and rules stay as written.
+## Reference files
+| File | What it answers |
+|------|-----------------|
+| `references/choosing-a-form.md` | Which chart type / is it even a chart? |
+| `references/color-formula.md` | The four jobs, the six checks, snap-to-passing |
+| `references/marks-and-anatomy.md` | Mark specs, spacers, labels, figures, hero number |
+| `references/interaction.md` | Tooltips &amp; hover, filters &amp; time ranges |
+| `references/components.md` | The pieces a chart is made of — build each in plain HTML |
+| `references/anti-patterns.md` | **What goes wrong — check every chart against this** |
+| `references/palette.md` | **The reference palette instance** — every parameter, filled in; swap for your brand's |
 | `scripts/validate_palette.js` | Runnable six-checks validator (run it; don't eyeball) |</t>
         </is>
       </c>
@@ -3382,7 +3382,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>done, cells: 2
+          <t>done, cells: 2
 valid json</t>
         </is>
       </c>
@@ -3413,7 +3413,7 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>done, cells: 2
+          <t>done, cells: 2
 valid json</t>
         </is>
       </c>
@@ -3858,8 +3858,8 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>appid,name,release_date,english,developer,publisher,platforms,required_age,categories,genres,steamspy_tags,achievements,positive_ratings,negative_ratings,average_playtime,median_playtime,owners,price
-10,Counter-Strike,2000-11-01,1,Valve,Valve,windows;mac;linux,0,Multi-player;Online Multi-Player;Local Multi-Player;Valve Anti-Cheat enabled,Action,Action;FPS;Multiplayer,0,124534,3339,17612,317,10000000-20000000,7.19
+          <t>appid,name,release_date,english,developer,publisher,platforms,required_age,categories,genres,steamspy_tags,achievements,positive_ratings,negative_ratings,average_playtime,median_playtime,owners,price
+10,Counter-Strike,2000-11-01,1,Valve,Valve,windows;mac;linux,0,Multi-player;Online Multi-Player;Local Multi-Player;Valve Anti-Cheat enabled,Action,Action;FPS;Multiplayer,0,124534,3339,17612,317,10000000-20000000,7.19
 ---rows---
 27076 steam.csv
 Shell cwd was reset to D:\Home\Unduhan Saya\study-package\tasks\task 2</t>
@@ -3892,8 +3892,8 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>appid,name,release_date,english,developer,publisher,platforms,required_age,categories,genres,steamspy_tags,achievements,positive_ratings,negative_ratings,average_playtime,median_playtime,owners,price
-10,Counter-Strike,2000-11-01,1,Valve,Valve,windows;mac;linux,0,Multi-player;Online Multi-Player;Local Multi-Player;Valve Anti-Cheat enabled,Action,Action;FPS;Multiplayer,0,124534,3339,17612,317,10000000-20000000,7.19
+          <t>appid,name,release_date,english,developer,publisher,platforms,required_age,categories,genres,steamspy_tags,achievements,positive_ratings,negative_ratings,average_playtime,median_playtime,owners,price
+10,Counter-Strike,2000-11-01,1,Valve,Valve,windows;mac;linux,0,Multi-player;Online Multi-Player;Local Multi-Player;Valve Anti-Cheat enabled,Action,Action;FPS;Multiplayer,0,124534,3339,17612,317,10000000-20000000,7.19
 ---rows---
 27076 steam.csv
 [stderr]
@@ -4175,8 +4175,8 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>--debug        output debug information about paths
-Available subcommands:
+          <t>--debug        output debug information about paths
+Available subcommands:
 Jupyter command `jupyter-nbconvert` not found.</t>
         </is>
       </c>
@@ -4207,8 +4207,8 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>--debug        output debug information about paths
-Available subcommands:
+          <t>--debug        output debug information about paths
+Available subcommands:
 Jupyter command `jupyter-nbconvert` not found.</t>
         </is>
       </c>
@@ -4299,9 +4299,9 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "&lt;string&gt;", line 1, in &lt;module&gt;
-ModuleNotFoundError: No module named 'nbclient'
+          <t>Traceback (most recent call last):
+  File "&lt;string&gt;", line 1, in &lt;module&gt;
+ModuleNotFoundError: No module named 'nbclient'
 deps ok</t>
         </is>
       </c>
@@ -4332,9 +4332,9 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "&lt;string&gt;", line 1, in &lt;module&gt;
-ModuleNotFoundError: No module named 'nbclient'
+          <t>Traceback (most recent call last):
+  File "&lt;string&gt;", line 1, in &lt;module&gt;
+ModuleNotFoundError: No module named 'nbclient'
 deps ok</t>
         </is>
       </c>
@@ -4425,9 +4425,9 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>[notice] A new release of pip is available: 26.0.1 -&gt; 26.1.2
-[notice] To update, run: python.exe -m pip install --upgrade pip
-Installed kernelspec python3 in C:\Users\sani2\AppData\Roaming\jupyter\kernels\python3
+          <t>[notice] A new release of pip is available: 26.0.1 -&gt; 26.1.2
+[notice] To update, run: python.exe -m pip install --upgrade pip
+Installed kernelspec python3 in C:\Users\sani2\AppData\Roaming\jupyter\kernels\python3
 DONE</t>
         </is>
       </c>
@@ -4458,9 +4458,9 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>[notice] A new release of pip is available: 26.0.1 -&gt; 26.1.2
-[notice] To update, run: python.exe -m pip install --upgrade pip
-Installed kernelspec python3 in C:\Users\sani2\AppData\Roaming\jupyter\kernels\python3
+          <t>[notice] A new release of pip is available: 26.0.1 -&gt; 26.1.2
+[notice] To update, run: python.exe -m pip install --upgrade pip
+Installed kernelspec python3 in C:\Users\sani2\AppData\Roaming\jupyter\kernels\python3
 DONE</t>
         </is>
       </c>
@@ -4521,9 +4521,9 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>C:\Users\sani2\AppData\Roaming\Python\Python310\site-packages\zmq\_future.py:718: RuntimeWarning: Proactor event loop does not implement add_reader family of methods required for zmq. Registering an additional selector thread for add_reader support via tornado. Use `asyncio.set_event_loop_policy(WindowsSelectorEventLoopPolicy())` to avoid this warning.
-  self._get_loop()
-[IPKernelApp] WARNING | Kernel is running over TCP without encryption. All communication (including code and outputs) is sent in plain text and is susceptible to eavesdropping. Use IPC transport or launch with kernel manager-provisioned CurveZMQ keys to enable transport encryption.
+          <t>C:\Users\sani2\AppData\Roaming\Python\Python310\site-packages\zmq\_future.py:718: RuntimeWarning: Proactor event loop does not implement add_reader family of methods required for zmq. Registering an additional selector thread for add_reader support via tornado. Use `asyncio.set_event_loop_policy(WindowsSelectorEventLoopPolicy())` to avoid this warning.
+  self._get_loop()
+[IPKernelApp] WARNING | Kernel is running over TCP without encryption. All communication (including code and outputs) is sent in plain text and is susceptible to eavesdropping. Use IPC transport or launch with kernel manager-provisioned CurveZMQ keys to enable transport encryption.
 EXECUTED OK</t>
         </is>
       </c>
@@ -4554,9 +4554,9 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>C:\Users\sani2\AppData\Roaming\Python\Python310\site-packages\zmq\_future.py:718: RuntimeWarning: Proactor event loop does not implement add_reader family of methods required for zmq. Registering an additional selector thread for add_reader support via tornado. Use `asyncio.set_event_loop_policy(WindowsSelectorEventLoopPolicy())` to avoid this warning.
-  self._get_loop()
-[IPKernelApp] WARNING | Kernel is running over TCP without encryption. All communication (including code and outputs) is sent in plain text and is susceptible to eavesdropping. Use IPC transport or launch with kernel manager-provisioned CurveZMQ keys to enable transport encryption.
+          <t>C:\Users\sani2\AppData\Roaming\Python\Python310\site-packages\zmq\_future.py:718: RuntimeWarning: Proactor event loop does not implement add_reader family of methods required for zmq. Registering an additional selector thread for add_reader support via tornado. Use `asyncio.set_event_loop_policy(WindowsSelectorEventLoopPolicy())` to avoid this warning.
+  self._get_loop()
+[IPKernelApp] WARNING | Kernel is running over TCP without encryption. All communication (including code and outputs) is sent in plain text and is susceptible to eavesdropping. Use IPC transport or launch with kernel manager-provisioned CurveZMQ keys to enable transport encryption.
 EXECUTED OK</t>
         </is>
       </c>
@@ -4647,18 +4647,18 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>exec_count: 1
-Loading...
-Loaded: (27075, 18)
-Games with &gt;=1 rating: 27075
-Games with &gt;= 1000 ratings: 2578
-Median price: 9.29
-Median positive review ratio: 0.8437
-Spearman r: -0.0085  p: 0.6665823689145232
-Pearson  r: -0.0565  p: 0.004125322243352175
-Final result (well-established games only):
-Spearman correlation between price and positive review ratio: -0.0085
-This is a negligible negative relationship: there is no meaningful evidence that more expensive games earn better user ratings.
+          <t>exec_count: 1
+Loading...
+Loaded: (27075, 18)
+Games with &gt;=1 rating: 27075
+Games with &gt;= 1000 ratings: 2578
+Median price: 9.29
+Median positive review ratio: 0.8437
+Spearman r: -0.0085  p: 0.6665823689145232
+Pearson  r: -0.0565  p: 0.004125322243352175
+Final result (well-established games only):
+Spearman correlation between price and positive review ratio: -0.0085
+This is a negligible negative relationship: there is no meaningful evidence that more expensive games earn better user ratings.
 FIGURE PRESENT: True</t>
         </is>
       </c>
@@ -4689,18 +4689,18 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>exec_count: 1
-Loading...
-Loaded: (27075, 18)
-Games with &gt;=1 rating: 27075
-Games with &gt;= 1000 ratings: 2578
-Median price: 9.29
-Median positive review ratio: 0.8437
-Spearman r: -0.0085  p: 0.6665823689145232
-Pearson  r: -0.0565  p: 0.004125322243352175
-Final result (well-established games only):
-Spearman correlation between price and positive review ratio: -0.0085
-This is a negligible negative relationship: there is no meaningful evidence that more expensive games earn better user ratings.
+          <t>exec_count: 1
+Loading...
+Loaded: (27075, 18)
+Games with &gt;=1 rating: 27075
+Games with &gt;= 1000 ratings: 2578
+Median price: 9.29
+Median positive review ratio: 0.8437
+Spearman r: -0.0085  p: 0.6665823689145232
+Pearson  r: -0.0565  p: 0.004125322243352175
+Final result (well-established games only):
+Spearman correlation between price and positive review ratio: -0.0085
+This is a negligible negative relationship: there is no meaningful evidence that more expensive games earn better user ratings.
 FIGURE PRESENT: True</t>
         </is>
       </c>
@@ -5951,194 +5951,194 @@
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20">
-        <f>=== CELL 0 markdown ====
-# Publisher Market Footprint and Genre Synergy
-The investment firm wants to evaluate PC game publishers for acquisition.
-The analysis has two components:
-- identify the publishers with the strongest **market footprint** in each genre;
-- determine which genres exhibit the strongest **operational synergies** across publisher portfolios.
-Market footprint is measured using estimated owners, which represents the publisher�s market reach within each genre.
-Genre synergy is measured using cosine similarity of publisher title-count portfolios. Genres with similar publisher title distributions are treated as having stronger operational synergy.
-The analysis therefore aggregates estimated owners by publisher and genre and constructs publisher title-count vectors for the genre comparison.
-==== CELL 1 code ====
-from __future__ import annotations
-import re
-from pathlib import Path
-import numpy as np
-import pandas as pd
-import matplotlib.pyplot as plt
-STEAM_PATH = Path("../../data/steam/steam.csv")
-TARGET_GENRES = [
-    "Action",
-    "Adventure",
-    "Casual",
-    "Indie",
-    "RPG",
-    "Strategy",
-    "Simulation",
-    "Sports",
-    "Racing",
-    "Free to Play",
-]
-def parse_owner_midpoint(value: object) -&gt; float:
-    """
-    Convert an owners interval such as
-    '1,000,000-2,000,000' into its midpoint.
-    """
-    if pd.isna(value):
-        return np.nan
-    cleaned = str(value).replace(",", "").strip()
-    match = re.fullmatch(
-        r"(\d+)\s*-\s*(\d+)",
-        cleaned,
-    )
-    if match is None:
-        return np.nan
-    lower = float(match.group(1))
-    upper = float(match.group(2))
-    return (lower + upper) / 2
-def cosine_similarity(
-    matrix: pd.DataFrame,
-) -&gt; pd.DataFrame:
-    values = matrix.to_numpy(dtype=float)
-    dot_products = values.T @ values
-    norms = np.sqrt(np.diag(dot_products))
-    denominator = np.outer(norms, norms)
-    similarities = np.divide(
-        dot_products,
-        denominator,
-        out=np.zeros_like(
-            dot_products,
-            dtype=float,
-        ),
-        where=denominator != 0,
-    )
-    np.fill_diagonal(
-        similarities,
-        1.0,
-    )
-    return pd.DataFrame(
-        similarities,
-        index=matrix.columns,
-        columns=matrix.columns,
-    )
-steam = pd.read_csv(STEAM_PATH)
-required_c
---OUT--
-Games in raw dataset: 27,075
-Game-publisher-genre assignments: 72,434
-Publishers analyzed: 14092
-==== CELL 2 code ====
-publisher_genre = (
-    long_data
-    .groupby(
-        [
-            "genre",
-            "publisher_name",
-        ],
-        as_index=False,
-    )
-    .agg(
-        estimated_owners=(
-            "owners_midpoint",
-            "sum",
-        ),
-        title_count=(
-            "appid",
-            "nunique",
-        ),
-    )
-)
-top_publishers = (
-    publisher_genre
-    .sort_values(
-        [
-            "genre",
-            "estimated_owners",
-        ],
-        ascending=[
-            True,
-            False,
-        ],
-    )
-    .groupby(
-        "genre",
-        group_keys=False,
-    )
-    .head(5)
-    .copy()
-)
-top_publishers["rank"] = (
-    top_publishers
-    .groupby("genre")
-    .cumcount()
-    + 1
-)
-genre_leaders = (
-    top_publishers[
-        top_publishers["rank"] == 1
-    ]
-)
-print(
-    "\nLeading publisher in each genre:"
-)
-print(
-    genre_leaders[
-        [
-            "genre",
-            "publisher_name",
-            "estimated_owners",
-        ]
-    ].to_string(index=False)
-)
-title_matrix = (
-    publisher_genre
-    .pivot(
-        index="publisher_name",
-        columns="genre",
-        values="title_count",
-    )
-    .fillna(0)
-    .reindex(
-        columns=TARGET_GENRES,
-        fill_value=0,
-    )
-)
-genre_synergy = cosine_similarity(
-    title_matrix
-)
-# Extract the upper triangle so each genre pair
-# appears only once and diagonal values are excluded.
-upper_triangle = np.triu(
-    np.ones(
-        genre_synergy.shape,
-        dtype=b
---OUT--
-Leading publisher in each genre:
-       genre        publisher_name  estimated_owners
-      Action                 Valve       492000000.0
-   Adventure      PUBG Corporation        75000000.0
-      Casual Smartly Dressed Games        35000000.0
-Free to Play                 Valve       260750000.0
-       Indie Smartly Dressed Games        35000000.0
-         RPG    Bethesda Softworks        45050000.0
-      Racing           Codemasters         9510000.0
-  Simulation   Paradox Interactive        23670000.0
-      Sports           Codemasters         9175000.0
-    Strategy                 Valve       151500000.0
-Most similar genre pairs:
-genre      genre     
-Adventure  Casual        0.724
-Action     Indie         0.639
-Strategy   Simulation    0.612
-Adventure  Indie         0.583
-Sports     Racing        0.581
---OUT--
-&lt;Figure size 800x700 with 2 Axes&gt;
-==== CELL 3 markdown ====
-## Conclusion
-The publisher rankings identify the publishers with the strongest market footprint in each genre based on estimated owners. These publishers represent the leading acquisition candidates within their respective market segments.
-The genre synergy matrix identifies genre pairs with similar publisher title-count portfolios. Genre pairs with the highest cosine similarity exhibit the strongest operational synergies because they are supported by similar publisher portfolio structures.
+        <f>=== CELL 0 markdown ====
+# Publisher Market Footprint and Genre Synergy
+The investment firm wants to evaluate PC game publishers for acquisition.
+The analysis has two components:
+- identify the publishers with the strongest **market footprint** in each genre;
+- determine which genres exhibit the strongest **operational synergies** across publisher portfolios.
+Market footprint is measured using estimated owners, which represents the publisher�s market reach within each genre.
+Genre synergy is measured using cosine similarity of publisher title-count portfolios. Genres with similar publisher title distributions are treated as having stronger operational synergy.
+The analysis therefore aggregates estimated owners by publisher and genre and constructs publisher title-count vectors for the genre comparison.
+==== CELL 1 code ====
+from __future__ import annotations
+import re
+from pathlib import Path
+import numpy as np
+import pandas as pd
+import matplotlib.pyplot as plt
+STEAM_PATH = Path("../../data/steam/steam.csv")
+TARGET_GENRES = [
+    "Action",
+    "Adventure",
+    "Casual",
+    "Indie",
+    "RPG",
+    "Strategy",
+    "Simulation",
+    "Sports",
+    "Racing",
+    "Free to Play",
+]
+def parse_owner_midpoint(value: object) -&gt; float:
+    """
+    Convert an owners interval such as
+    '1,000,000-2,000,000' into its midpoint.
+    """
+    if pd.isna(value):
+        return np.nan
+    cleaned = str(value).replace(",", "").strip()
+    match = re.fullmatch(
+        r"(\d+)\s*-\s*(\d+)",
+        cleaned,
+    )
+    if match is None:
+        return np.nan
+    lower = float(match.group(1))
+    upper = float(match.group(2))
+    return (lower + upper) / 2
+def cosine_similarity(
+    matrix: pd.DataFrame,
+) -&gt; pd.DataFrame:
+    values = matrix.to_numpy(dtype=float)
+    dot_products = values.T @ values
+    norms = np.sqrt(np.diag(dot_products))
+    denominator = np.outer(norms, norms)
+    similarities = np.divide(
+        dot_products,
+        denominator,
+        out=np.zeros_like(
+            dot_products,
+            dtype=float,
+        ),
+        where=denominator != 0,
+    )
+    np.fill_diagonal(
+        similarities,
+        1.0,
+    )
+    return pd.DataFrame(
+        similarities,
+        index=matrix.columns,
+        columns=matrix.columns,
+    )
+steam = pd.read_csv(STEAM_PATH)
+required_c
+--OUT--
+Games in raw dataset: 27,075
+Game-publisher-genre assignments: 72,434
+Publishers analyzed: 14092
+==== CELL 2 code ====
+publisher_genre = (
+    long_data
+    .groupby(
+        [
+            "genre",
+            "publisher_name",
+        ],
+        as_index=False,
+    )
+    .agg(
+        estimated_owners=(
+            "owners_midpoint",
+            "sum",
+        ),
+        title_count=(
+            "appid",
+            "nunique",
+        ),
+    )
+)
+top_publishers = (
+    publisher_genre
+    .sort_values(
+        [
+            "genre",
+            "estimated_owners",
+        ],
+        ascending=[
+            True,
+            False,
+        ],
+    )
+    .groupby(
+        "genre",
+        group_keys=False,
+    )
+    .head(5)
+    .copy()
+)
+top_publishers["rank"] = (
+    top_publishers
+    .groupby("genre")
+    .cumcount()
+    + 1
+)
+genre_leaders = (
+    top_publishers[
+        top_publishers["rank"] == 1
+    ]
+)
+print(
+    "\nLeading publisher in each genre:"
+)
+print(
+    genre_leaders[
+        [
+            "genre",
+            "publisher_name",
+            "estimated_owners",
+        ]
+    ].to_string(index=False)
+)
+title_matrix = (
+    publisher_genre
+    .pivot(
+        index="publisher_name",
+        columns="genre",
+        values="title_count",
+    )
+    .fillna(0)
+    .reindex(
+        columns=TARGET_GENRES,
+        fill_value=0,
+    )
+)
+genre_synergy = cosine_similarity(
+    title_matrix
+)
+# Extract the upper triangle so each genre pair
+# appears only once and diagonal values are excluded.
+upper_triangle = np.triu(
+    np.ones(
+        genre_synergy.shape,
+        dtype=b
+--OUT--
+Leading publisher in each genre:
+       genre        publisher_name  estimated_owners
+      Action                 Valve       492000000.0
+   Adventure      PUBG Corporation        75000000.0
+      Casual Smartly Dressed Games        35000000.0
+Free to Play                 Valve       260750000.0
+       Indie Smartly Dressed Games        35000000.0
+         RPG    Bethesda Softworks        45050000.0
+      Racing           Codemasters         9510000.0
+  Simulation   Paradox Interactive        23670000.0
+      Sports           Codemasters         9175000.0
+    Strategy                 Valve       151500000.0
+Most similar genre pairs:
+genre      genre     
+Adventure  Casual        0.724
+Action     Indie         0.639
+Strategy   Simulation    0.612
+Adventure  Indie         0.583
+Sports     Racing        0.581
+--OUT--
+&lt;Figure size 800x700 with 2 Axes&gt;
+==== CELL 3 markdown ====
+## Conclusion
+The publisher rankings identify the publishers with the strongest market footprint in each genre based on estimated owners. These publishers represent the leading acquisition candidates within their respective market segments.
+The genre synergy matrix identifies genre pairs with similar publisher title-count portfolios. Genre pairs with the highest cosine similarity exhibit the strongest operational synergies because they are supported by similar publisher portfolio structures.
 The investment firm should prioritize the highest-ranked publishers in each genre, particularly publishers operating across the genre pairs with the highest similarity scores.</f>
         <v/>
       </c>
@@ -6168,194 +6168,194 @@
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21">
-        <f>=== CELL 0 markdown ====
-# Publisher Market Footprint and Genre Synergy
-The investment firm wants to evaluate PC game publishers for acquisition.
-The analysis has two components:
-- identify the publishers with the strongest **market footprint** in each genre;
-- determine which genres exhibit the strongest **operational synergies** across publisher portfolios.
-Market footprint is measured using estimated owners, which represents the publisher�s market reach within each genre.
-Genre synergy is measured using cosine similarity of publisher title-count portfolios. Genres with similar publisher title distributions are treated as having stronger operational synergy.
-The analysis therefore aggregates estimated owners by publisher and genre and constructs publisher title-count vectors for the genre comparison.
-==== CELL 1 code ====
-from __future__ import annotations
-import re
-from pathlib import Path
-import numpy as np
-import pandas as pd
-import matplotlib.pyplot as plt
-STEAM_PATH = Path("../../data/steam/steam.csv")
-TARGET_GENRES = [
-    "Action",
-    "Adventure",
-    "Casual",
-    "Indie",
-    "RPG",
-    "Strategy",
-    "Simulation",
-    "Sports",
-    "Racing",
-    "Free to Play",
-]
-def parse_owner_midpoint(value: object) -&gt; float:
-    """
-    Convert an owners interval such as
-    '1,000,000-2,000,000' into its midpoint.
-    """
-    if pd.isna(value):
-        return np.nan
-    cleaned = str(value).replace(",", "").strip()
-    match = re.fullmatch(
-        r"(\d+)\s*-\s*(\d+)",
-        cleaned,
-    )
-    if match is None:
-        return np.nan
-    lower = float(match.group(1))
-    upper = float(match.group(2))
-    return (lower + upper) / 2
-def cosine_similarity(
-    matrix: pd.DataFrame,
-) -&gt; pd.DataFrame:
-    values = matrix.to_numpy(dtype=float)
-    dot_products = values.T @ values
-    norms = np.sqrt(np.diag(dot_products))
-    denominator = np.outer(norms, norms)
-    similarities = np.divide(
-        dot_products,
-        denominator,
-        out=np.zeros_like(
-            dot_products,
-            dtype=float,
-        ),
-        where=denominator != 0,
-    )
-    np.fill_diagonal(
-        similarities,
-        1.0,
-    )
-    return pd.DataFrame(
-        similarities,
-        index=matrix.columns,
-        columns=matrix.columns,
-    )
-steam = pd.read_csv(STEAM_PATH)
-required_c
---OUT--
-Games in raw dataset: 27,075
-Game-publisher-genre assignments: 72,434
-Publishers analyzed: 14092
-==== CELL 2 code ====
-publisher_genre = (
-    long_data
-    .groupby(
-        [
-            "genre",
-            "publisher_name",
-        ],
-        as_index=False,
-    )
-    .agg(
-        estimated_owners=(
-            "owners_midpoint",
-            "sum",
-        ),
-        title_count=(
-            "appid",
-            "nunique",
-        ),
-    )
-)
-top_publishers = (
-    publisher_genre
-    .sort_values(
-        [
-            "genre",
-            "estimated_owners",
-        ],
-        ascending=[
-            True,
-            False,
-        ],
-    )
-    .groupby(
-        "genre",
-        group_keys=False,
-    )
-    .head(5)
-    .copy()
-)
-top_publishers["rank"] = (
-    top_publishers
-    .groupby("genre")
-    .cumcount()
-    + 1
-)
-genre_leaders = (
-    top_publishers[
-        top_publishers["rank"] == 1
-    ]
-)
-print(
-    "\nLeading publisher in each genre:"
-)
-print(
-    genre_leaders[
-        [
-            "genre",
-            "publisher_name",
-            "estimated_owners",
-        ]
-    ].to_string(index=False)
-)
-title_matrix = (
-    publisher_genre
-    .pivot(
-        index="publisher_name",
-        columns="genre",
-        values="title_count",
-    )
-    .fillna(0)
-    .reindex(
-        columns=TARGET_GENRES,
-        fill_value=0,
-    )
-)
-genre_synergy = cosine_similarity(
-    title_matrix
-)
-# Extract the upper triangle so each genre pair
-# appears only once and diagonal values are excluded.
-upper_triangle = np.triu(
-    np.ones(
-        genre_synergy.shape,
-        dtype=b
---OUT--
-Leading publisher in each genre:
-       genre        publisher_name  estimated_owners
-      Action                 Valve       492000000.0
-   Adventure      PUBG Corporation        75000000.0
-      Casual Smartly Dressed Games        35000000.0
-Free to Play                 Valve       260750000.0
-       Indie Smartly Dressed Games        35000000.0
-         RPG    Bethesda Softworks        45050000.0
-      Racing           Codemasters         9510000.0
-  Simulation   Paradox Interactive        23670000.0
-      Sports           Codemasters         9175000.0
-    Strategy                 Valve       151500000.0
-Most similar genre pairs:
-genre      genre     
-Adventure  Casual        0.724
-Action     Indie         0.639
-Strategy   Simulation    0.612
-Adventure  Indie         0.583
-Sports     Racing        0.581
---OUT--
-&lt;Figure size 800x700 with 2 Axes&gt;
-==== CELL 3 markdown ====
-## Conclusion
-The publisher rankings identify the publishers with the strongest market footprint in each genre based on estimated owners. These publishers represent the leading acquisition candidates within their respective market segments.
-The genre synergy matrix identifies genre pairs with similar publisher title-count portfolios. Genre pairs with the highest cosine similarity exhibit the strongest operational synergies because they are supported by similar publisher portfolio structures.
+        <f>=== CELL 0 markdown ====
+# Publisher Market Footprint and Genre Synergy
+The investment firm wants to evaluate PC game publishers for acquisition.
+The analysis has two components:
+- identify the publishers with the strongest **market footprint** in each genre;
+- determine which genres exhibit the strongest **operational synergies** across publisher portfolios.
+Market footprint is measured using estimated owners, which represents the publisher�s market reach within each genre.
+Genre synergy is measured using cosine similarity of publisher title-count portfolios. Genres with similar publisher title distributions are treated as having stronger operational synergy.
+The analysis therefore aggregates estimated owners by publisher and genre and constructs publisher title-count vectors for the genre comparison.
+==== CELL 1 code ====
+from __future__ import annotations
+import re
+from pathlib import Path
+import numpy as np
+import pandas as pd
+import matplotlib.pyplot as plt
+STEAM_PATH = Path("../../data/steam/steam.csv")
+TARGET_GENRES = [
+    "Action",
+    "Adventure",
+    "Casual",
+    "Indie",
+    "RPG",
+    "Strategy",
+    "Simulation",
+    "Sports",
+    "Racing",
+    "Free to Play",
+]
+def parse_owner_midpoint(value: object) -&gt; float:
+    """
+    Convert an owners interval such as
+    '1,000,000-2,000,000' into its midpoint.
+    """
+    if pd.isna(value):
+        return np.nan
+    cleaned = str(value).replace(",", "").strip()
+    match = re.fullmatch(
+        r"(\d+)\s*-\s*(\d+)",
+        cleaned,
+    )
+    if match is None:
+        return np.nan
+    lower = float(match.group(1))
+    upper = float(match.group(2))
+    return (lower + upper) / 2
+def cosine_similarity(
+    matrix: pd.DataFrame,
+) -&gt; pd.DataFrame:
+    values = matrix.to_numpy(dtype=float)
+    dot_products = values.T @ values
+    norms = np.sqrt(np.diag(dot_products))
+    denominator = np.outer(norms, norms)
+    similarities = np.divide(
+        dot_products,
+        denominator,
+        out=np.zeros_like(
+            dot_products,
+            dtype=float,
+        ),
+        where=denominator != 0,
+    )
+    np.fill_diagonal(
+        similarities,
+        1.0,
+    )
+    return pd.DataFrame(
+        similarities,
+        index=matrix.columns,
+        columns=matrix.columns,
+    )
+steam = pd.read_csv(STEAM_PATH)
+required_c
+--OUT--
+Games in raw dataset: 27,075
+Game-publisher-genre assignments: 72,434
+Publishers analyzed: 14092
+==== CELL 2 code ====
+publisher_genre = (
+    long_data
+    .groupby(
+        [
+            "genre",
+            "publisher_name",
+        ],
+        as_index=False,
+    )
+    .agg(
+        estimated_owners=(
+            "owners_midpoint",
+            "sum",
+        ),
+        title_count=(
+            "appid",
+            "nunique",
+        ),
+    )
+)
+top_publishers = (
+    publisher_genre
+    .sort_values(
+        [
+            "genre",
+            "estimated_owners",
+        ],
+        ascending=[
+            True,
+            False,
+        ],
+    )
+    .groupby(
+        "genre",
+        group_keys=False,
+    )
+    .head(5)
+    .copy()
+)
+top_publishers["rank"] = (
+    top_publishers
+    .groupby("genre")
+    .cumcount()
+    + 1
+)
+genre_leaders = (
+    top_publishers[
+        top_publishers["rank"] == 1
+    ]
+)
+print(
+    "\nLeading publisher in each genre:"
+)
+print(
+    genre_leaders[
+        [
+            "genre",
+            "publisher_name",
+            "estimated_owners",
+        ]
+    ].to_string(index=False)
+)
+title_matrix = (
+    publisher_genre
+    .pivot(
+        index="publisher_name",
+        columns="genre",
+        values="title_count",
+    )
+    .fillna(0)
+    .reindex(
+        columns=TARGET_GENRES,
+        fill_value=0,
+    )
+)
+genre_synergy = cosine_similarity(
+    title_matrix
+)
+# Extract the upper triangle so each genre pair
+# appears only once and diagonal values are excluded.
+upper_triangle = np.triu(
+    np.ones(
+        genre_synergy.shape,
+        dtype=b
+--OUT--
+Leading publisher in each genre:
+       genre        publisher_name  estimated_owners
+      Action                 Valve       492000000.0
+   Adventure      PUBG Corporation        75000000.0
+      Casual Smartly Dressed Games        35000000.0
+Free to Play                 Valve       260750000.0
+       Indie Smartly Dressed Games        35000000.0
+         RPG    Bethesda Softworks        45050000.0
+      Racing           Codemasters         9510000.0
+  Simulation   Paradox Interactive        23670000.0
+      Sports           Codemasters         9175000.0
+    Strategy                 Valve       151500000.0
+Most similar genre pairs:
+genre      genre     
+Adventure  Casual        0.724
+Action     Indie         0.639
+Strategy   Simulation    0.612
+Adventure  Indie         0.583
+Sports     Racing        0.581
+--OUT--
+&lt;Figure size 800x700 with 2 Axes&gt;
+==== CELL 3 markdown ====
+## Conclusion
+The publisher rankings identify the publishers with the strongest market footprint in each genre based on estimated owners. These publishers represent the leading acquisition candidates within their respective market segments.
+The genre synergy matrix identifies genre pairs with similar publisher title-count portfolios. Genre pairs with the highest cosine similarity exhibit the strongest operational synergies because they are supported by similar publisher portfolio structures.
 The investment firm should prioritize the highest-ranked publishers in each genre, particularly publishers operating across the genre pairs with the highest similarity scores.</f>
         <v/>
       </c>
@@ -8134,9 +8134,9 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "&lt;string&gt;", line 1, in &lt;module&gt;
-ModuleNotFoundError: No module named 'nbconvert'
+          <t>Traceback (most recent call last):
+  File "&lt;string&gt;", line 1, in &lt;module&gt;
+ModuleNotFoundError: No module named 'nbconvert'
 NBCONVERT_MISSING
 PANDAS_OK</t>
         </is>
@@ -8168,9 +8168,9 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Traceback (most recent call last):
-  File "&lt;string&gt;", line 1, in &lt;module&gt;
-ModuleNotFoundError: No module named 'nbconvert'
+          <t>Traceback (most recent call last):
+  File "&lt;string&gt;", line 1, in &lt;module&gt;
+ModuleNotFoundError: No module named 'nbconvert'
 NBCONVERT_MISSING
 PANDAS_OK</t>
         </is>
@@ -8262,13 +8262,13 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Valve games: 30
-Average price: $4.48
-Median price: $3.99
-Dominant genre: Action (26 games)
-Highest positive-rating percentage: Portal 2 (98.65%)
-=== analysis done ===
-&lt;IPython.core.display.HTML object&gt;
+          <t>Valve games: 30
+Average price: $4.48
+Median price: $3.99
+Dominant genre: Action (26 games)
+Highest positive-rating percentage: Portal 2 (98.65%)
+=== analysis done ===
+&lt;IPython.core.display.HTML object&gt;
 === card html written to valve_card.html ===</t>
         </is>
       </c>
@@ -8299,13 +8299,13 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Valve games: 30
-Average price: $4.48
-Median price: $3.99
-Dominant genre: Action (26 games)
-Highest positive-rating percentage: Portal 2 (98.65%)
-=== analysis done ===
-&lt;IPython.core.display.HTML object&gt;
+          <t>Valve games: 30
+Average price: $4.48
+Median price: $3.99
+Dominant genre: Action (26 games)
+Highest positive-rating percentage: Portal 2 (98.65%)
+=== analysis done ===
+&lt;IPython.core.display.HTML object&gt;
 === card html written to valve_card.html ===</t>
         </is>
       </c>
